--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/02_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/02_NovatedApp_Regression.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762AEA13-F122-4636-953E-BA605742C117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F7F86F-BBF7-4B22-B384-2AD18F512DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="120">
   <si>
     <t>TC ID</t>
   </si>
@@ -140,9 +140,6 @@
     <t>End Of Lease Date</t>
   </si>
   <si>
-    <t>30/08/2029 10:00 GMT+10:00</t>
-  </si>
-  <si>
     <t>Submitted By</t>
   </si>
   <si>
@@ -335,21 +332,9 @@
     <t>AAI Limited (Vero Insurance)</t>
   </si>
   <si>
-    <t>22 May 2026</t>
-  </si>
-  <si>
     <t>$1,000.00</t>
   </si>
   <si>
-    <t>12346</t>
-  </si>
-  <si>
-    <t>REQ-783</t>
-  </si>
-  <si>
-    <t>12347</t>
-  </si>
-  <si>
     <t>0469750861</t>
   </si>
   <si>
@@ -359,73 +344,55 @@
     <t>29/07/2026</t>
   </si>
   <si>
-    <t>01/06/2026</t>
-  </si>
-  <si>
-    <t>REQ-784</t>
-  </si>
-  <si>
-    <t>12348</t>
-  </si>
-  <si>
-    <t>REQ-785</t>
-  </si>
-  <si>
-    <t>12349</t>
-  </si>
-  <si>
-    <t>REQ-786</t>
-  </si>
-  <si>
-    <t>12364</t>
-  </si>
-  <si>
-    <t>REQ-814</t>
-  </si>
-  <si>
-    <t>12365</t>
-  </si>
-  <si>
-    <t>REQ-815</t>
-  </si>
-  <si>
-    <t>12366</t>
-  </si>
-  <si>
-    <t>REQ-816</t>
-  </si>
-  <si>
-    <t>12367</t>
-  </si>
-  <si>
-    <t>REQ-817</t>
-  </si>
-  <si>
-    <t>12378</t>
-  </si>
-  <si>
-    <t>23 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-829</t>
-  </si>
-  <si>
-    <t>12379</t>
-  </si>
-  <si>
-    <t>REQ-830</t>
-  </si>
-  <si>
-    <t>12380</t>
-  </si>
-  <si>
-    <t>REQ-831</t>
-  </si>
-  <si>
-    <t>12381</t>
-  </si>
-  <si>
-    <t>REQ-832</t>
+    <t>30 Aug 2029</t>
+  </si>
+  <si>
+    <t>2 Jun 2026</t>
+  </si>
+  <si>
+    <t>${TC001.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC003.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC005.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC007.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>5576</t>
+  </si>
+  <si>
+    <t>REQ-946</t>
+  </si>
+  <si>
+    <t>5577</t>
+  </si>
+  <si>
+    <t>REQ-947</t>
+  </si>
+  <si>
+    <t>5578</t>
+  </si>
+  <si>
+    <t>REQ-948</t>
+  </si>
+  <si>
+    <t>09/06/2026</t>
+  </si>
+  <si>
+    <t>Submitted By1</t>
+  </si>
+  <si>
+    <t>5581</t>
+  </si>
+  <si>
+    <t>REQ-951</t>
+  </si>
+  <si>
+    <t>${TC003.New Registration Expiry Date}</t>
   </si>
 </sst>
 </file>
@@ -853,38 +820,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AV10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="8.5"/>
-    <col min="2" max="2" customWidth="true" width="20.625"/>
-    <col min="3" max="4" customWidth="true" width="24.375"/>
-    <col min="5" max="5" customWidth="true" width="27.375"/>
-    <col min="6" max="6" customWidth="true" width="16.75"/>
-    <col min="7" max="7" customWidth="true" width="15.375"/>
-    <col min="8" max="8" customWidth="true" width="21.75"/>
-    <col min="9" max="9" customWidth="true" width="18.625"/>
-    <col min="10" max="10" customWidth="true" width="23.75"/>
-    <col min="11" max="11" customWidth="true" width="17.25"/>
-    <col min="12" max="12" customWidth="true" width="19.875"/>
-    <col min="13" max="13" customWidth="true" width="20.625"/>
-    <col min="14" max="14" customWidth="true" width="17.5"/>
-    <col min="15" max="15" customWidth="true" width="14.625"/>
-    <col min="16" max="16" customWidth="true" width="19.375"/>
-    <col min="17" max="17" customWidth="true" width="18.5"/>
-    <col min="18" max="22" customWidth="true" width="19.125"/>
-    <col min="23" max="23" customWidth="true" width="25.625"/>
-    <col min="24" max="24" customWidth="true" style="4" width="27.125"/>
-    <col min="25" max="25" customWidth="true" width="25.375"/>
-    <col min="26" max="26" customWidth="true" width="19.5"/>
-    <col min="27" max="27" customWidth="true" width="14.5"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="4" width="17.25"/>
-    <col min="29" max="29" customWidth="true" style="4" width="15.125"/>
-    <col min="47" max="48" bestFit="true" customWidth="true" style="4" width="9.375"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" width="9.375"/>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="4" width="24.375" customWidth="1"/>
+    <col min="5" max="5" width="27.375" customWidth="1"/>
+    <col min="6" max="6" width="16.75" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="8" width="21.75" customWidth="1"/>
+    <col min="9" max="9" width="18.625" customWidth="1"/>
+    <col min="10" max="10" width="23.75" customWidth="1"/>
+    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="12" max="12" width="19.875" customWidth="1"/>
+    <col min="13" max="13" width="19.375" customWidth="1"/>
+    <col min="14" max="14" width="18.5" customWidth="1"/>
+    <col min="15" max="19" width="19.125" customWidth="1"/>
+    <col min="20" max="20" width="25.625" customWidth="1"/>
+    <col min="21" max="21" width="27.125" style="4" customWidth="1"/>
+    <col min="22" max="22" width="25.375" customWidth="1"/>
+    <col min="23" max="23" width="19.5" customWidth="1"/>
+    <col min="24" max="24" width="14.5" customWidth="1"/>
+    <col min="25" max="25" width="17.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.125" style="4" customWidth="1"/>
+    <col min="46" max="47" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="1" customFormat="1" ht="60">
+    <row r="1" spans="1:48" s="1" customFormat="1" ht="60">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -922,118 +886,115 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE1" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG1" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI1" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM1" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO1" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="AP1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG1" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH1" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI1" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ1" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK1" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AL1" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM1" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN1" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO1" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AQ1" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="AR1" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AS1" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="AT1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="AU1" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AW1" s="11" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" spans="1:49" s="2" customFormat="1" ht="40.5">
+    <row r="2" spans="1:48" s="2" customFormat="1" ht="40.5">
       <c r="A2" s="7" t="s">
         <v>22</v>
       </c>
@@ -1041,21 +1002,21 @@
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="D2" s="8">
         <f>C2+1</f>
-        <v>12379.0</v>
-      </c>
-      <c r="E2" s="8" t="n">
+        <v>5577</v>
+      </c>
+      <c r="E2" s="8">
         <f>C2+1</f>
-        <v>12379.0</v>
+        <v>5577</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>32</v>
@@ -1064,7 +1025,7 @@
         <v>24</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>24</v>
@@ -1082,62 +1043,67 @@
         <v>24</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>123</v>
+        <v>110</v>
+      </c>
+      <c r="S2" s="9" t="str">
+        <f>TEXT(E2,"#,##0")&amp;" km"</f>
+        <v>5,577 km</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="V2" s="9" t="str">
-        <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>12,379 km</v>
+        <v>103</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X2" s="7"/>
-      <c r="Y2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z2" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
       <c r="AD2" s="7"/>
-      <c r="AE2" s="7"/>
+      <c r="AE2" s="12"/>
       <c r="AF2" s="7"/>
-      <c r="AG2" s="7"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="7"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="7"/>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="12"/>
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="12"/>
       <c r="AL2" s="12"/>
-      <c r="AM2" s="7"/>
-      <c r="AN2" s="12"/>
-      <c r="AO2" s="12"/>
-      <c r="AP2" s="7"/>
-      <c r="AQ2" s="7"/>
+      <c r="AM2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ2" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="AR2" s="12"/>
       <c r="AS2" s="12"/>
       <c r="AT2" s="12"/>
       <c r="AU2" s="12"/>
       <c r="AV2" s="12"/>
-      <c r="AW2" s="12"/>
     </row>
-    <row r="3" spans="1:49" s="2" customFormat="1" ht="54">
+    <row r="3" spans="1:48" s="2" customFormat="1" ht="54">
       <c r="A3" s="7" t="s">
         <v>25</v>
       </c>
@@ -1152,10 +1118,10 @@
         <v>27</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>32</v>
@@ -1164,7 +1130,7 @@
         <v>24</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>24</v>
@@ -1182,119 +1148,116 @@
         <v>24</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="W3" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z3" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
       <c r="AA3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="AD3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AE3" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="AF3" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG3" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AH3" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AG3" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AJ3" s="12" t="s">
+      <c r="AH3" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AI3" s="12" t="s">
         <v>88</v>
       </c>
+      <c r="AJ3" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK3" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="AL3" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AM3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN3" s="12" t="s">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="AN3" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="AO3" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AP3" s="7" t="s">
-        <v>37</v>
+      <c r="AP3" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="AQ3" s="12" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="AR3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS3" s="12" t="s">
-        <v>92</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AS3" s="12"/>
       <c r="AT3" s="12"/>
       <c r="AU3" s="12"/>
       <c r="AV3" s="12"/>
-      <c r="AW3" s="12"/>
     </row>
-    <row r="4" spans="1:49" s="2" customFormat="1" ht="27">
+    <row r="4" spans="1:48" s="2" customFormat="1" ht="40.5">
       <c r="A4" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="D4" s="8">
         <f>C4+1</f>
-        <v>12380.0</v>
-      </c>
-      <c r="E4" s="8" t="n">
+        <v>5582</v>
+      </c>
+      <c r="E4" s="8">
         <f>C4+1</f>
-        <v>12380.0</v>
+        <v>5582</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>32</v>
@@ -1321,84 +1284,89 @@
         <v>24</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>123</v>
+        <v>118</v>
+      </c>
+      <c r="S4" s="9" t="str">
+        <f>TEXT(E4,"#,##0")&amp;" km"</f>
+        <v>5,582 km</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="V4" s="9" t="str">
-        <f>TEXT(E4,"#,##0")&amp;" km"</f>
-        <v>12,380 km</v>
+        <v>103</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X4" s="7"/>
-      <c r="Y4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7"/>
-      <c r="AE4" s="7"/>
+      <c r="AE4" s="12"/>
       <c r="AF4" s="7"/>
-      <c r="AG4" s="7"/>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="7"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="7"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="7"/>
+      <c r="AI4" s="12"/>
+      <c r="AJ4" s="7"/>
+      <c r="AK4" s="12"/>
       <c r="AL4" s="12"/>
-      <c r="AM4" s="7"/>
-      <c r="AN4" s="12"/>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="7"/>
-      <c r="AQ4" s="7"/>
+      <c r="AM4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO4" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP4" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ4" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="AR4" s="12"/>
       <c r="AS4" s="12"/>
-      <c r="AT4" s="12"/>
-      <c r="AU4" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="14" t="s">
-        <v>108</v>
+      <c r="AT4" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU4" s="12"/>
+      <c r="AV4" s="14" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:49" s="2" customFormat="1" ht="54">
+    <row r="5" spans="1:48" s="2" customFormat="1" ht="81">
       <c r="A5" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>32</v>
@@ -1425,127 +1393,124 @@
         <v>24</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="AB5" s="7" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AE5" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="AF5" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG5" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AH5" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI5" s="7" t="s">
+      <c r="AG5" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AJ5" s="12" t="s">
+      <c r="AH5" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AK5" s="7" t="s">
+      <c r="AI5" s="12" t="s">
         <v>88</v>
       </c>
+      <c r="AJ5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK5" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="AL5" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AM5" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN5" s="12" t="s">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="AN5" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="AO5" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AP5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ5" s="7" t="s">
-        <v>92</v>
+      <c r="AP5" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ5" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="AR5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS5" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="14" t="s">
-        <v>108</v>
+        <v>91</v>
+      </c>
+      <c r="AS5" s="12"/>
+      <c r="AT5" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU5" s="12"/>
+      <c r="AV5" s="7" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:49" s="2" customFormat="1" ht="67.5">
+    <row r="6" spans="1:48" s="2" customFormat="1" ht="67.5">
       <c r="A6" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="D6" s="8">
         <f>C6+1</f>
-        <v>12381.0</v>
-      </c>
-      <c r="E6" s="8" t="n">
+        <v>5578</v>
+      </c>
+      <c r="E6" s="8">
         <f>C6+1</f>
-        <v>12381.0</v>
+        <v>5578</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>32</v>
@@ -1572,86 +1537,91 @@
         <v>24</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>123</v>
+        <v>112</v>
+      </c>
+      <c r="S6" s="9" t="str">
+        <f>TEXT(E6,"#,##0")&amp;" km"</f>
+        <v>5,578 km</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="V6" s="9" t="str">
-        <f>TEXT(E6,"#,##0")&amp;" km"</f>
-        <v>12,381 km</v>
+        <v>103</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X6" s="7"/>
-      <c r="Y6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z6" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
-      <c r="AE6" s="7"/>
+      <c r="AE6" s="12"/>
       <c r="AF6" s="7"/>
-      <c r="AG6" s="7"/>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="7"/>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="7"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="12"/>
+      <c r="AJ6" s="7"/>
+      <c r="AK6" s="12"/>
       <c r="AL6" s="12"/>
-      <c r="AM6" s="7"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="7"/>
-      <c r="AQ6" s="7"/>
+      <c r="AM6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO6" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP6" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ6" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="AR6" s="12"/>
-      <c r="AS6" s="12"/>
-      <c r="AT6" s="12" t="s">
-        <v>98</v>
+      <c r="AS6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT6" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="AU6" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV6" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AW6" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="AV6" s="14"/>
     </row>
-    <row r="7" spans="1:49" s="2" customFormat="1" ht="67.5">
+    <row r="7" spans="1:48" s="2" customFormat="1" ht="67.5">
       <c r="A7" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>32</v>
@@ -1678,125 +1648,122 @@
         <v>24</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="V7" s="7" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z7" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
       <c r="AA7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB7" s="7"/>
-      <c r="AC7" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="AB7" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC7" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="AD7" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE7" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AE7" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="AF7" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG7" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AH7" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI7" s="7" t="s">
+      <c r="AG7" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AJ7" s="12" t="s">
+      <c r="AH7" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AK7" s="7" t="s">
+      <c r="AI7" s="12" t="s">
         <v>88</v>
       </c>
+      <c r="AJ7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK7" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="AL7" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AM7" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN7" s="12" t="s">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="AN7" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="AO7" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AP7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ7" s="7" t="s">
-        <v>92</v>
+      <c r="AP7" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ7" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="AR7" s="12" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="AS7" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT7" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="AT7" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="AU7" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV7" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AW7" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="AV7" s="14"/>
     </row>
-    <row r="8" spans="1:49" s="2" customFormat="1" ht="67.5">
+    <row r="8" spans="1:48" s="2" customFormat="1" ht="67.5">
       <c r="A8" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="D8" s="8">
         <f>C8+1</f>
-        <v>12382.0</v>
-      </c>
-      <c r="E8" s="8" t="n">
+        <v>5579</v>
+      </c>
+      <c r="E8" s="8">
         <f>C8+1</f>
-        <v>12382.0</v>
+        <v>5579</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>32</v>
@@ -1823,86 +1790,91 @@
         <v>24</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" s="7" t="s">
-        <v>123</v>
+        <v>114</v>
+      </c>
+      <c r="S8" s="9" t="str">
+        <f>TEXT(E8,"#,##0")&amp;" km"</f>
+        <v>5,579 km</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="V8" s="9" t="str">
-        <f>TEXT(E8,"#,##0")&amp;" km"</f>
-        <v>12,382 km</v>
+        <v>103</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X8" s="7"/>
-      <c r="Y8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z8" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
       <c r="AB8" s="7"/>
       <c r="AC8" s="7"/>
       <c r="AD8" s="7"/>
-      <c r="AE8" s="7"/>
+      <c r="AE8" s="12"/>
       <c r="AF8" s="7"/>
-      <c r="AG8" s="7"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="7"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="7"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="12"/>
       <c r="AL8" s="12"/>
-      <c r="AM8" s="7"/>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="7"/>
-      <c r="AQ8" s="7"/>
+      <c r="AM8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO8" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP8" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ8" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="AR8" s="12"/>
-      <c r="AS8" s="12"/>
-      <c r="AT8" s="12" t="s">
-        <v>99</v>
+      <c r="AS8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AT8" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="AU8" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV8" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AW8" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="AV8" s="14"/>
     </row>
-    <row r="9" spans="1:49" s="2" customFormat="1" ht="67.5">
+    <row r="9" spans="1:48" s="2" customFormat="1" ht="67.5">
       <c r="A9" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>32</v>
@@ -1929,106 +1901,103 @@
         <v>24</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z9" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
       <c r="AA9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC9" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="AD9" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE9" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="AE9" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="AF9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AH9" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI9" s="7" t="s">
+      <c r="AG9" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AJ9" s="12" t="s">
+      <c r="AH9" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AK9" s="7" t="s">
+      <c r="AI9" s="12" t="s">
         <v>88</v>
       </c>
+      <c r="AJ9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK9" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="AL9" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AM9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN9" s="12" t="s">
-        <v>90</v>
+        <v>36</v>
+      </c>
+      <c r="AN9" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="AO9" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AP9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ9" s="7" t="s">
-        <v>92</v>
+      <c r="AP9" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ9" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="AR9" s="12" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="AS9" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT9" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+      <c r="AT9" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="AU9" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV9" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AW9" s="14"/>
+        <v>102</v>
+      </c>
+      <c r="AV9" s="14"/>
     </row>
-    <row r="10" spans="1:49" ht="15">
-      <c r="U10" s="3"/>
+    <row r="10" spans="1:48" ht="15">
+      <c r="R10" s="3"/>
+      <c r="AU10" s="13"/>
       <c r="AV10" s="13"/>
-      <c r="AW10" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
